--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="333">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -526,6 +526,132 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationType</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -536,10 +662,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Description narrative de l'observation</t>
   </si>
   <si>
@@ -686,123 +808,34 @@
     <t>Observation.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -1339,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK84"/>
+  <dimension ref="A1:AK95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
@@ -4040,7 +4073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -4059,7 +4092,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4354,7 +4387,9 @@
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4371,10 +4406,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4400,13 +4437,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4424,7 +4459,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4444,16 +4479,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
       </c>
@@ -4470,13 +4507,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4527,7 +4562,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4545,28 +4580,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -4575,11 +4610,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4606,11 +4641,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4628,7 +4665,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4648,17 +4685,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4676,11 +4713,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4707,11 +4744,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4729,7 +4768,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4749,17 +4788,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
@@ -4777,7 +4816,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
@@ -4850,7 +4889,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>182</v>
       </c>
@@ -4871,7 +4910,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4880,7 +4919,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
@@ -4911,29 +4950,31 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4953,18 +4994,16 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -4981,11 +5020,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5036,7 +5075,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5056,18 +5095,16 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5084,11 +5121,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5115,11 +5152,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5137,7 +5176,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5157,16 +5196,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5183,10 +5224,12 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5212,29 +5255,31 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5254,21 +5299,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5280,17 +5327,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L39" t="s" s="2">
         <v>200</v>
       </c>
+      <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5339,46 +5382,46 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5387,11 +5430,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5442,13 +5485,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5462,18 +5505,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5490,12 +5531,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5545,7 +5584,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5565,10 +5604,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5591,13 +5630,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5624,11 +5663,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5646,7 +5687,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5666,10 +5707,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5767,17 +5808,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5799,7 +5840,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5811,7 +5852,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5826,13 +5867,11 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>74</v>
+        <v>215</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5850,7 +5889,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5870,23 +5909,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5898,11 +5937,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5953,7 +5992,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5973,23 +6012,23 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
@@ -6001,11 +6040,11 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6032,13 +6071,11 @@
         <v>74</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -6056,7 +6093,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6076,23 +6113,23 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -6104,11 +6141,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6159,7 +6196,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6179,23 +6216,23 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -6207,11 +6244,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6238,13 +6275,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6262,7 +6297,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6282,10 +6317,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6308,12 +6343,10 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>238</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6339,13 +6372,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6363,7 +6394,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6383,10 +6414,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6411,11 +6442,15 @@
       <c r="K50" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L50" s="2"/>
+      <c r="L50" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="M50" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -6482,7 +6517,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>244</v>
       </c>
@@ -6500,10 +6535,10 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -6512,11 +6547,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6567,7 +6602,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6587,23 +6622,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6615,7 +6650,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
@@ -6676,7 +6711,7 @@
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6688,7 +6723,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>253</v>
       </c>
@@ -6699,30 +6734,30 @@
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" t="s" s="2">
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6749,13 +6784,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6773,36 +6806,38 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
@@ -6810,7 +6845,7 @@
         <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6819,13 +6854,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>260</v>
+        <v>86</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6852,13 +6885,11 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -6876,7 +6907,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>257</v>
+        <v>89</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6896,16 +6927,18 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E55" s="2"/>
+      <c r="E55" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
@@ -6922,10 +6955,12 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6936,7 +6971,7 @@
         <v>74</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>74</v>
+        <v>258</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>74</v>
@@ -6951,11 +6986,13 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>263</v>
+        <v>74</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6973,7 +7010,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6991,26 +7028,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>74</v>
@@ -7019,10 +7058,12 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>265</v>
+        <v>112</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
+      <c r="M56" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7072,7 +7113,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>264</v>
+        <v>173</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7092,21 +7133,23 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -7118,10 +7161,12 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7147,11 +7192,13 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>267</v>
+        <v>74</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7169,7 +7216,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7187,26 +7234,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>74</v>
@@ -7215,13 +7264,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7272,13 +7319,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>268</v>
+        <v>181</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -7290,26 +7337,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7318,13 +7367,11 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7351,11 +7398,13 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>274</v>
+        <v>74</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7373,13 +7422,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7391,12 +7440,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7410,7 +7459,7 @@
         <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -7419,13 +7468,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7452,11 +7499,13 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7474,13 +7523,13 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>74</v>
@@ -7494,10 +7543,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7520,13 +7569,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7577,13 +7624,13 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
@@ -7597,21 +7644,23 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" s="2"/>
+      <c r="E62" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -7623,10 +7672,12 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
+      <c r="M62" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7676,7 +7727,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>281</v>
+        <v>197</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7696,21 +7747,23 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7722,10 +7775,12 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
+      <c r="M63" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -7775,7 +7830,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>283</v>
+        <v>202</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7795,21 +7850,23 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -7821,10 +7878,12 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>286</v>
+        <v>161</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
+      <c r="M64" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -7874,7 +7933,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>285</v>
+        <v>206</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7892,12 +7951,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7911,7 +7970,7 @@
         <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -7920,13 +7979,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7977,13 +8036,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -7997,10 +8056,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8011,7 +8070,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8023,7 +8082,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8052,13 +8111,11 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>74</v>
+        <v>274</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8076,13 +8133,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8094,12 +8151,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8110,10 +8167,10 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>74</v>
@@ -8122,7 +8179,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8175,13 +8232,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -8195,10 +8252,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8209,7 +8266,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8221,7 +8278,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>296</v>
+        <v>91</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8250,13 +8307,11 @@
         <v>74</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>74</v>
@@ -8274,13 +8329,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8292,12 +8347,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8311,7 +8366,7 @@
         <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
@@ -8320,10 +8375,14 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8373,7 +8432,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8391,12 +8450,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8407,10 +8466,10 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -8419,10 +8478,14 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8448,13 +8511,11 @@
         <v>74</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8472,7 +8533,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8490,12 +8551,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8506,10 +8567,10 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -8518,10 +8579,14 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8547,13 +8612,11 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>74</v>
+        <v>288</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8571,7 +8634,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8591,10 +8654,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8605,7 +8668,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8617,11 +8680,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="L72" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="M72" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8672,7 +8737,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8692,18 +8757,16 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
@@ -8720,12 +8783,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>85</v>
+        <v>293</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8751,11 +8812,13 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8773,7 +8836,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8793,10 +8856,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8819,12 +8882,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8874,7 +8935,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>93</v>
+        <v>294</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8894,10 +8955,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8908,7 +8969,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -8920,12 +8981,10 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>95</v>
+        <v>297</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -8975,19 +9034,19 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>97</v>
+        <v>296</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>74</v>
@@ -8995,18 +9054,16 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
@@ -9023,11 +9080,13 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L76" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="M76" t="s" s="2">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9054,11 +9113,13 @@
         <v>74</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>74</v>
@@ -9076,13 +9137,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>89</v>
+        <v>298</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9096,23 +9157,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9124,12 +9183,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>303</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9179,13 +9236,13 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>104</v>
+        <v>302</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>74</v>
@@ -9199,23 +9256,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E78" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9227,12 +9282,10 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>305</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9282,13 +9335,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>109</v>
+        <v>304</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9302,23 +9355,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9330,12 +9381,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9343,7 +9392,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>74</v>
@@ -9385,13 +9434,13 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>115</v>
+        <v>306</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>74</v>
@@ -9405,23 +9454,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9433,12 +9480,10 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>102</v>
+        <v>309</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9488,13 +9533,13 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>119</v>
+        <v>308</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
@@ -9508,10 +9553,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9534,12 +9579,10 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9589,7 +9632,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>125</v>
+        <v>310</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9609,10 +9652,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9623,7 +9666,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>74</v>
@@ -9635,7 +9678,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>85</v>
+        <v>313</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9646,7 +9689,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>316</v>
+        <v>74</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>74</v>
@@ -9664,11 +9707,13 @@
         <v>74</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>317</v>
+        <v>74</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -9686,13 +9731,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9706,10 +9751,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9717,10 +9762,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9732,10 +9777,12 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -9785,13 +9832,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9805,21 +9852,23 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9831,10 +9880,12 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -9860,13 +9911,11 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -9884,26 +9933,1137 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
+      <c r="B87" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y87" s="2"/>
+      <c r="Z87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L89" s="2"/>
+      <c r="M89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L91" s="2"/>
+      <c r="M91" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK84" t="s" s="2">
+      <c r="H92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y93" s="2"/>
+      <c r="Z93" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK95" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK84">
+  <autoFilter ref="A1:AK95">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9913,7 +11073,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
